--- a/data/trans_orig/P21D_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_1_R-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos en 2023</t>
+          <t>Población que, necesitando atención sanitaria médica, no la pudo recibir por motivos económicos en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,97 +730,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1735</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>298176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>564546</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1073,97 +1073,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2960</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1217</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446138</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1103868</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1416,97 +1416,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3537</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>713</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3633</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3611</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4743</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>328822</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325757</t>
+          <t>325853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>655484</t>
+          <t>656616</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,97 +1759,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3288</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3983</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3674</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,07%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3522</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>406119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>513959</t>
+          <t>514654</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922373</t>
+          <t>922221</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2102,97 +2102,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1400</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4422</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5358</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5380</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1661591</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1589552</t>
+          <t>1589548</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3252372</t>
+          <t>3252394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P21D_1_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P21D_1_R-Habitat-trans_orig.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>266599</t>
+          <t>288123</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>299287</t>
+          <t>324160</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>565886</t>
+          <t>612283</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>658389</t>
+          <t>470208</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>447355</t>
+          <t>503394</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1105744</t>
+          <t>973601</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3830</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>749</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>4348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1559,27 +1559,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>328677</t>
+          <t>377900</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325853</t>
+          <t>374819</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1594,27 +1594,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>659514</t>
+          <t>754483</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>656616</t>
+          <t>750884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>330838</t>
+          <t>376584</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>329390</t>
+          <t>378649</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>660227</t>
+          <t>755232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1799,12 +1799,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>702</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3552</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1902,27 +1902,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>517255</t>
+          <t>490032</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>514654</t>
+          <t>487226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1937,27 +1937,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>925208</t>
+          <t>923391</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>922221</t>
+          <t>920541</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>407953</t>
+          <t>433359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>517942</t>
+          <t>490734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>925895</t>
+          <t>924093</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4426</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,7 +2167,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1400</t>
+          <t>1451</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5358</t>
+          <t>5120</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2245,17 +2245,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1592574</t>
+          <t>1695485</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1589548</t>
+          <t>1691587</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2280,17 +2280,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3256352</t>
+          <t>3263759</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3252394</t>
+          <t>3260090</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1663778</t>
+          <t>1568274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1593974</t>
+          <t>1696936</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3257752</t>
+          <t>3265210</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
